--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0014.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0014.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Sát Thương Liên Tục Five Thunders Spell Array</t>
+          <t>Sát Thương Liên Tục Bát Quái Ngũ Lôi Trận</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Tiêu hao STA của Heavy Attack</t>
+          <t>HA Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sát Thương Nhấn</t>
+          <t>Tấn công gây DMG.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Giữ để Dodge</t>
+          <t>Giữ để Né Tránh</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Concerto Regen Nhấn</t>
+          <t>Kích hoạt Concerto Regen nào.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Concerto Regen Giữ</t>
+          <t>Giữ Hồi Phục Concerto</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Sát Thương Linh Hồn Inklit</t>
+          <t>DMG Tâm Linh Mực Tím</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Tiêu Hao STA Phép Thuật Heavy Attack</t>
+          <t>HA - Tiêu Hao STA Phép Thuật</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Sát Thương Thiên Tài Bất Chợt</t>
+          <t>Sát Thương Nét Thiên Tài</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Sát Thương Đỉnh Cao Sáng Tạo</t>
+          <t>DMG Bản Giao Hưởng Sáng Tạo Cực Đỉnh</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Concerto Regen Đỉnh Cao Sáng Tạo</t>
+          <t>Hồi phục Bản Giao Hưởng Sáng Tạo Cực Đỉnh</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Concerto Regen Nhấn Giữa Không Trung</t>
+          <t>Hồi Phục Concerto khi Nhấn trên không</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Heavy Attack: Sát Thương Băng Giá</t>
+          <t>Đòn Heavy Attack: Frostfall DMG</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Bói Kiếm Quyển - Healing</t>
+          <t>Bói Kiếm Quyển - Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Sát Thương Tiếng Kêu</t>
+          <t>Sát Thương Bản Giao Hưởng</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sát Thương Như Ý</t>
+          <t>Sát Thương Bản Giao Hưởng Ruyi</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Sát Thương Mask</t>
+          <t>Sát Thương Mặt Nạ</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Concerto Regen Chuông</t>
+          <t>Hồi Phục Hòa Tấu Chuông</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Concerto Regen Như Ý</t>
+          <t>Hồi Phục Bản Giao Hưởng Ruyi</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Hồi Phục Bản Giao Hưởng Mask</t>
+          <t>Hồi Phục Bản Giao Hưởng Mặt Nạ</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>DMG kỹ năng Poetic Essence</t>
+          <t>Sát Thương Kỹ Năng Bản Chất Thi Ca</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Healing Bản Chất Thi Ca</t>
+          <t>Hồi Phục Bản Chất Thi Ca</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Tăng Gấp Đôi Healing Khi Đánh Trúng</t>
+          <t>Tăng Gấp Đôi Hồi Phục Khi Đánh Trúng</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Stage 1 Basic Attack</t>
+          <t>Giai Đoạn 1 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 1 Necessary Measures</t>
+          <t>Giai Đoạn 1 Sát Thương Biện Pháp Cần Thiết</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 2 Necessary Measures</t>
+          <t>Giai Đoạn 2 Sát Thương Biện Pháp Cần Thiết</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 3 Necessary Measures</t>
+          <t>Giai Đoạn 3 Sát Thương Biện Pháp Cần Thiết</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Sát Thương Tactics Kiểm Soát</t>
+          <t>Sát Thương Chiến Thuật Kiểm Soát</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>DMG Customary Greetings</t>
+          <t>Sát Thương Lời Chào Thông Thường</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>DMG Chromatic Splendor</t>
+          <t>Sát Thương Sắc Màu Rực Rỡ</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Concerto Regen Chromatic Splendor</t>
+          <t>Hòa Tấu Phục Hồi Sắc Màu Rực Rỡ</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>DMG Death Knell</t>
+          <t>Sát Thương Chuông Tử Thần</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>DMG Fatal Finale</t>
+          <t>Sát Thương Khúc Kết Tử</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Cooldown Skill</t>
+          <t>Thời gian hồi Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Concerto Regen Death Knell</t>
+          <t>Khúc Tái Sinh Chuông Tử Thần</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Concerto Regen Fatal Finale</t>
+          <t>Hồi Phục Khúc Kết Tử</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Thời gian Deconstruction</t>
+          <t>Thời gian phân rã</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Thời gian Twilight Tango</t>
+          <t>Thời Gian Khiêu Vũ Hoàng Hôn</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>DMG Imminent Oblivion</t>
+          <t>Sát Thương Hư Vô Sắp Đến</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Cooldown Tinted Crystal</t>
+          <t>Thời gian hồi Pha Lê Nhuộm Màu</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Concerto Regen Imminent Oblivion</t>
+          <t>Khúc Tái Sinh Cận Kề Của Bản Giao Hưởng Vô Minh</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Thời gian Moldable Crystal</t>
+          <t>Thời Gian Tạo Hình Pha Lê</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Khúc Giao Hưởng Tactics Kiểm Soát Regen</t>
+          <t>Khúc Giao Hưởng Chiến Thuật Kiểm Soát Regen</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>DMG Woolies</t>
+          <t>Sát Thương Lông Xù</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>DMG Flaming Woolies</t>
+          <t>Sát Thương Cừu Lông Cháy</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>DMG Energetic Welcome</t>
+          <t>Sát Thương Chào Mừng Đầy Hứng Khởi</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Concerto Regen Flaming Woolies</t>
+          <t>Hồi Phục Bản Giao Hưởng Cừu Lông Cháy</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Concerto Regen Energetic Welcome</t>
+          <t>Hồi Phục Nhạc Đoạn Chào Mừng Đầy Hứng Khởi</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 1 Cosmos: Frolicking</t>
+          <t>Cosmos: Sát Thương Giai Đoạn 1 - Đùa Nghịch</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 2 Cosmos: Frolicking</t>
+          <t>Cosmos: Sát Thương Giai Đoạn 2 - Đùa Nghịch</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 3 Cosmos: Flee</t>
+          <t>Cosmos: Sát Thương Giai Đoạn 3 Vui Đùa</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Cosmos: Sát Thương Heavy Attack</t>
+          <t>Cosmos: Heavy Attack DMG</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Cosmos: Tiêu Hao Thể Lực Heavy Attack</t>
+          <t>Cosmos: Heavy Attack STA Cost</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Sát Thương Cơn Cuồng Cosmos</t>
+          <t>Sát Thương Cơn Cuồng Vũ Trụ</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Cooldown Phục Cơn Cuồng Cosmos</t>
+          <t>Thời gian hồi Phục Cơn Cuồng Vũ Trụ</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>DMG Dodge Counter Cosmos</t>
+          <t>Cosmos: Dodge Counter DMG</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Thời Gian Điệu Nhảy Cosmos</t>
+          <t>Thời Gian Điệu Nhảy Vũ Trụ</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Sát Thương Bản Hoà Tấu Cuồng Loạn: Cloudy</t>
+          <t>Sát Thương Bản Hoà Tấu Cuồng Loạn: U Ám</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Sát Thương Vỡ Cosmos</t>
+          <t>Sát Thương Vỡ Vũ Trụ</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Hồi Phục Bản Hoà Tấu Cuồng Loạn: Cloudy</t>
+          <t>Hồi Phục Bản Hoà Tấu Cuồng Loạn: U Ám</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Hồi Phục Bản Giao Hưởng Vỡ Cosmos</t>
+          <t>Hồi Phục Bản Giao Hưởng Vỡ Vũ Trụ</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Giai đoạn 3 Basic Attack: Mayhem</t>
+          <t>Cú Đòn Cơ Bản Hạng 3: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Giai đoạn 4 Basic Attack: Mayhem</t>
+          <t>Cú Đòn Cơ Bản Hạng 4: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Woolies: Mayhem</t>
+          <t>Woolies: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Heavy Attack: Hỗn Loạn</t>
+          <t>Đòn Heavy Attack: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Woolies Helpers: Mayhem</t>
+          <t>Trợ Thủ Lông Xù: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Flaming Woolies: Mayhem</t>
+          <t>Cừu Lông Cháy: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Energetic Welcome: Mayhem</t>
+          <t>Chào Mừng Đầy Hứng Khởi: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Giai đoạn 1 Cosmos: Frolicking: Mayhem</t>
+          <t>Cosmos: Giai Đoạn 1 - Đùa Nghịch: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Giai đoạn 2 Cosmos: Frolicking: Mayhem</t>
+          <t>Cosmos: Giai Đoạn 2 Vui Đùa: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Giai đoạn 3 Cosmos: Frolicking: Mayhem</t>
+          <t>Cosmos: Giai Đoạn 3 Vui Đùa: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Giai đoạn 4 Cosmos: Frolicking: Mayhem</t>
+          <t>Cosmos: Giai Đoạn 4 Vui Đùa: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Cosmos: Heavy Attack: Hỗn Loạn</t>
+          <t>Cosmos: Heavy Attack: Mayhem</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sát Thương Bản Giao Hưởng Sấm Trên Núi</t>
+          <t>Tấn Công Mạnh - Sát Thương Bản Giao Hưởng Sấm Trên Núi</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Heavy Attack - Healing Bản Giao Hưởng Song Núi</t>
+          <t>Tấn Công Mạnh - Hồi Phục Bản Giao Hưởng Song Núi</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Heavy Attack - Bản Giao Hưởng Sấm Trên Núi Tiêu Hao STA</t>
+          <t>Tấn Công Mạnh - Bản Giao Hưởng Sấm Trên Núi Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực - Heavy Attack Song Sơn</t>
+          <t>Chi phí STA - Đòn Heavy Attack Song Sơn</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực - Khúc Giao Hưởng Sấm Sét Đôi</t>
+          <t>Chi phí STA - Khúc Giao Hưởng Sấm Sét Đôi</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Heavy Attack - Bản Giao Hưởng Sấm Trên Núi Hồi Phục</t>
+          <t>Tấn Công Mạnh - Bản Giao Hưởng Sấm Trên Núi Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Heavy Attack - Bản Giao Hưởng Song Núi Hồi Phục</t>
+          <t>Tấn Công Mạnh - Bản Giao Hưởng Song Núi Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>DMG liên tục hiệu ứng Pull-in</t>
+          <t>Sát Thương Kéo Liên Tục</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>DMG kỹ năng Flashing Thunder Spell</t>
+          <t>Sát Thương Phép Thuật Sấm Chớp</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Healing Skill</t>
+          <t>Hồi Phục Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Sát thương Attack 1 Basic 1</t>
+          <t>DMG Basic Attack 1</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack 2</t>
+          <t>DMG Basic Attack 2</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack 3</t>
+          <t>DMG Basic Attack 3</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack 4</t>
+          <t>DMG Basic Attack 4</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Sát thương Attack 1 Trên Không 1</t>
+          <t>DMG Mid-air Attack 1</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Sát thương Mid-air Attack 2</t>
+          <t>DMG Mid-air Attack 2</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Sát thương Mid-air Attack 3</t>
+          <t>DMG Mid-air Attack 3</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Sát thương Mid-air Attack 4</t>
+          <t>DMG Mid-air Attack 4</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Heavy Attack Trên Không</t>
+          <t>Đòn Tấn Công Mạnh Trên Không</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Tiêu Hao STA Heavy Attack Trên Không</t>
+          <t>Tiêu Hao STA Đòn Tấn Công Mạnh Trên Không</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>True Sight: Sát Thương Thu Hồi</t>
+          <t>Thị Lực Chân Thật: Capture DMG</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>True Sight: Sát Thương Chinh Phục</t>
+          <t>Thị Lực Chân Thật: Conquest DMG</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>True Sight: Sát Thương Tích Lũy</t>
+          <t>Thị Lực Chân Thật: Charge DMG</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>True Sight: Thu Hồi - Khúc Tái Sinh</t>
+          <t>Thị Lực Chân Thật: Capture - Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>True Sight: Conquest - Khúc Tái Sinh</t>
+          <t>Thị Lực Chân Thật: Conquest - Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>True Sight: Charge - Khúc Tái Sinh</t>
+          <t>Thị Lực Chân Thật: Charge - Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Sát Thương Flaming Sacrifice</t>
+          <t>Sát Thương Hy Sinh Lửa Cháy</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Sát Thương Chém Stage 1 Mid-air Attack</t>
+          <t>Sát Thương Chém Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Concerto Regen Returned from Ashes</t>
+          <t>Hồi phục từ Ashes Concerto</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Thời Gian Shield</t>
+          <t>Thời Gian Khiên</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack - Gặm Nhấm Của Sói</t>
+          <t>Sát Thương Đòn Heavy Attack - Gặm Nhấm Của Sói</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Stage 2 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 2 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Stage 3 Đòn Mid-air Attack: Sát Thương</t>
+          <t>Giai Đoạn 3 Đòn Mid-air Attack: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Sát Thương Đòn Đánh Lửa</t>
+          <t>Tấn Công Giữa Không - Sát Thương Đòn Đánh Lửa</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Sát Thương Plunging Attack</t>
+          <t>Sát Thương Tấn Công Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Chi Phí Thể Lực Heavy Attack - Gặm Nhấm Của Sói</t>
+          <t>Chi Phí STA Đòn Heavy Attack - Gặm Nhấm Của Sói</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực - Vuốt Sói</t>
+          <t>Chi phí STA - Vuốt Sói</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tiêu Hao Thể Lực Plunging Attack</t>
+          <t>Tiêu Hao STA Tấn Công Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Tiêu Hao STA Đòn Đánh Lửa</t>
+          <t>Tấn Công Giữa Không - Tiêu Hao STA Đòn Đánh Lửa</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>DMG kỹ năng</t>
+          <t>Sát thương Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>DMG Feral Fang</t>
+          <t>Sát Thương Nanh Hoang</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>DMG Dance With the Wolf</t>
+          <t>Vũ điệu Sát Thương Sói</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Vũ điệu Sát Thương Sói: Cao Trào</t>
+          <t>Vũ điệu Sát Thương Sói: Climax DMG</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>DMG Set the Arena Ablaze</t>
+          <t>Gây Sát Thương Thiêu Đốt Đấu Trường</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>DMG kỹ năng</t>
+          <t>Sát thương Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>DMG Foebreaker</t>
+          <t>DMG Phá Kẻ Thù</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Thời Gian Burning Matchpoint</t>
+          <t>Thời Gian Điểm Hỏa Cháy</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>DMG kỹ năng</t>
+          <t>Sát thương Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>DMG Nowhere to Run!</t>
+          <t>Không đường thoát! Sát Thương</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Concerto Regen Nowhere to Run!</t>
+          <t>Không đường thoát! Concerto Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 1 Basic Attack</t>
+          <t>DMG Giai đoạn 1 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 2 Basic Attack</t>
+          <t>DMG Giai đoạn 2 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 3 Basic Attack</t>
+          <t>DMG Giai đoạn 3 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 4 của Basic Attack</t>
+          <t>Sát Thương Cú Đòn Cơ Bản Hạng 4</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Dodge Counter - Sát thương Máu Đổi Máu</t>
+          <t>Phản đòn né tránh - DMG Máu Đổi Máu</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Sát Thương Lao Xuống Ashfall Barrage</t>
+          <t>Tấn Công Giữa Không - Sát Thương Lao Xuống Ashfall Barrage</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Sát Thương Duy Trì Ashfall Barrage</t>
+          <t>Tấn Công Giữa Không - Sát Thương Duy Trì Ashfall Barrage</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Stage 1 DMG - Loạt Đòn Tử Thần</t>
+          <t>Sát Thương Giai Đoạn 1 - Loạt Đòn Tử Thần</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Stage 2 DMG - Loạt Đòn Tử Thần</t>
+          <t>Sát Thương Giai Đoạn 2 - Loạt Đòn Tử Thần</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Stage 3 DMG - Loạt Đòn Tử Thần</t>
+          <t>Sát Thương Giai Đoạn 3 - Loạt Đòn Tử Thần</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Intro Skill - Sát Thương Vụ Nổ Hỏa Ngục</t>
+          <t>Kỹ Năng Khởi Động - Sát Thương Vụ Nổ Hỏa Ngục</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>DMG Outro Skill</t>
+          <t>Sát Thương Kỹ Năng Hồi Kết</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>DMG Hellstride</t>
+          <t>Sát Thương Bước Nhảy Địa Ngục</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Heavy Attack - Stage 1 DMG Phán Quyết Cánh Lửa</t>
+          <t>Tấn Công Mạnh - Sát Thương Giai Đoạn 1 Phán Quyết Cánh Lửa</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Heavy Attack - Stage 2 DMG Phán Quyết Cánh Lửa</t>
+          <t>Tấn Công Mạnh - Sát Thương Giai Đoạn 2 Phán Quyết Cánh Lửa</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Heavy Attack - Stage 3 DMG Phán Quyết Cánh Lửa</t>
+          <t>Tấn Công Mạnh - Sát Thương Giai Đoạn 3 Phán Quyết Cánh Lửa</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Dodge Counter - Purgatory Scourge</t>
+          <t>Né Tránh Phản Công - Lưỡi Trảm Địa Ngục</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Resonance Skill - Xâm Lấn: Cooldown</t>
+          <t>Resonance Skill - Xâm Lấn: Hồi Chiêu</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Loạt Attack Tro Tàn Tiêu Hao STA (Mỗi Giây)</t>
+          <t>Tấn Công Giữa Không - Loạt Tấn Công Tro Tàn Tiêu Hao STA (Mỗi Giây)</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Tiêu hao STA Ashfall Barrage</t>
+          <t>Tấn Công Giữa Không - Tiêu hao STA Ashfall Barrage</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực Stage 1 - Loạt Đòn Tử Thần</t>
+          <t>Chi phí STA Giai Đoạn 1 - Loạt Đòn Tử Thần</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực Stage 2 - Loạt Đòn Tử Thần</t>
+          <t>Chi phí STA Giai Đoạn 2 - Loạt Đòn Tử Thần</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực Stage 3 - Loạt Đòn Tử Thần</t>
+          <t>Chi phí STA Giai Đoạn 3 - Loạt Đòn Tử Thần</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Resonance Liberation - Bản Giao Hưởng Xá Tội Hỏa Ngục Resonance Cost</t>
+          <t>Resonance Liberation - Bản Giao Hưởng Xá Tội Hỏa Ngục Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Intro Skill - Bản Giao Hưởng Quá Tải Hỏa Diêm</t>
+          <t>Kỹ Năng Khởi Động - Bản Giao Hưởng Quá Tải Hỏa Diêm</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Resonance Liberation - Bản Giao Hưởng Xá Tội Hỏa Ngục Cooldown</t>
+          <t>Resonance Liberation - Bản Giao Hưởng Xá Tội Hỏa Ngục Hồi Chiêu</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Heavy Attack - Tiêu hao Thể Lực Stage 1 Phán Quyết Cánh Lửa</t>
+          <t>Tấn Công Mạnh - Tiêu hao STA Giai Đoạn 1 Phán Quyết Cánh Lửa</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Heavy Attack - Tiêu hao Thể Lực Stage 2 Phán Quyết Cánh Lửa</t>
+          <t>Tấn Công Mạnh - Tiêu hao STA Giai Đoạn 2 Phán Quyết Cánh Lửa</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Heavy Attack - Tiêu hao Thể Lực Stage 3 Phán Quyết Cánh Lửa</t>
+          <t>Tấn Công Mạnh - Tiêu hao STA Giai Đoạn 3 Phán Quyết Cánh Lửa</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Resonance Skill - Khúc Dâng Oán Thù: Thời Gian Cooldown</t>
+          <t>Resonance Skill - Khúc Dâng Oán Thù: Thời gian hồi Chiêu</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Tiêu hao STA Hellstride</t>
+          <t>Tiêu Hao STA Bước Nhảy Địa Ngục</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Loạt Đòn Địa Ngục Sát Thương Đâm Xuống</t>
+          <t>Tấn Công Giữa Không - Loạt Đòn Địa Ngục Sát Thương Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Loạt Đòn Địa Ngục Lửa Liên Tục Sát Thương</t>
+          <t>Tấn Công Giữa Không - Loạt Đòn Địa Ngục Lửa Liên Tục Sát Thương</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Loạt Đòn Địa Ngục Lửa Liên Tục Tiêu Hao STA (Mỗi Giây)</t>
+          <t>Tấn Công Giữa Không - Loạt Đòn Địa Ngục Lửa Liên Tục Tiêu Hao STA (Mỗi Giây)</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Loạt Đòn Địa Ngục Tiêu Hao STA</t>
+          <t>Tấn Công Giữa Không - Loạt Đòn Địa Ngục Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Resonance Skill - Tàn Phá: Cooldown</t>
+          <t>Resonance Skill - Tàn Phá: Hồi Chiêu</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 1 Extermination Order</t>
+          <t>Sát Thương Giai Đoạn 1 Lệnh Tiêu Diệt</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 2 Extermination Order</t>
+          <t>Sát Thương Giai Đoạn 2 Lệnh Tiêu Diệt</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>DMG giai đoạn 3 Extermination Order</t>
+          <t>Sát Thương Giai Đoạn 3 Lệnh Tiêu Diệt</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Giai đoạn 1 Hounds Roar</t>
+          <t>Gầm Thét Của Hound Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Giai đoạn 2 Hounds Roar</t>
+          <t>Gầm Thét Của Hound Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Giai đoạn 3 Hounds Roar</t>
+          <t>Gầm Thét Của Hound Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Giai đoạn 4 Hounds Roar</t>
+          <t>Gầm Thét Của Hound Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Giai đoạn 5 Hounds Roar</t>
+          <t>Gầm Thét Của Hound Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Thời gian Deathblade Gear</t>
+          <t>Thời Gian Hoạt Động Kiếm Tử Thần</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>"Mercy" Gây Sát Thương</t>
+          <t>"Lòng thương xót" Gây Sát Thương</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>"Sát Thương "Messenger Tử Thần""</t>
+          <t>"Sát Thương "Sứ Giả Tử Thần""</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>DMG "Necessary Means"</t>
+          <t>"Sát Thương 'Biện Pháp Cần Thiết'"</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Extermination Order Concerto Regen</t>
+          <t>Hồi Phục Concerto Lệnh Tiêu Diệt</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>"Mercy" Concerto Regen</t>
+          <t>"Lòng thương xót" Hồi Phục Concerto</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Tiêu hao Thể lực cho Heavy Attack</t>
+          <t>Tiêu hao STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>DMG Chameleon Cipher</t>
+          <t>Sát Thương Mật Mã Biến Hình</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>DMG Magnetic Roar</t>
+          <t>Sát Thương Hống Magnet</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>DMG Lightning Execution</t>
+          <t>Sát Thương Khúc Hành Quyết Sét</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>DMG Electromagnetic Blast</t>
+          <t>Sát Thương Khúc Nổ Điện Từ</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>DMG Judgment Strike</t>
+          <t>Sát Thương Đòn Phán Xét</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Thời gian</t>
+          <t>Thời lượng</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Thời gian Chế độ Execution</t>
+          <t>Thời gian Chế độ Thi hành án</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Sát Thương Attack Phối Hợp Nêm Lôi</t>
+          <t>Sát Thương Tấn Công Phối Hợp Nêm Lôi</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>DMG Thunder Wedge Detonation</t>
+          <t>Sát Thương Nổ Nêm Lôi</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>DMG Rumbling Spark</t>
+          <t>Sát Thương Bản Giao Hưởng Tia Lửa Âm Thanh</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>DMG Thunder Uprising</t>
+          <t>Sát Thương Nổi Dậy Của Sấm</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Thời gian Thunder Wedge</t>
+          <t>Thời Gian Tồn Tại Nêm Lôi</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Basic Attack Tích Điện</t>
+          <t>Sát Thương Giai Đoạn 1 Đòn Cơ Bản Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Stage 2 DMG Basic Attack Tích Điện</t>
+          <t>Sát Thương Giai Đoạn 2 Đòn Cơ Bản Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Stage 3 DMG Basic Attack Tích Điện</t>
+          <t>Sát Thương Giai Đoạn 3 Đòn Cơ Bản Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Stage 4 DMG Basic Attack Tích Điện</t>
+          <t>Sát Thương Giai Đoạn 4 Đòn Cơ Bản Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Stage 5 DMG Basic Attack Tích Điện</t>
+          <t>Sát Thương Giai Đoạn 5 Đòn Cơ Bản Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack Tích Điện</t>
+          <t>Sát Thương Đòn Heavy Attack Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>DMG Thunderweaver</t>
+          <t>Sát Thương Dệt Sấm</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Chi Phí Thể Lực Heavy Attack Tích Điện</t>
+          <t>Chi Phí STA Đòn Heavy Attack Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG (Nhiễm Lôi)</t>
+          <t>Sát Thương Né Tránh Phản Đòn Tích Điện</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Thời gian Nhiễm Lôi</t>
+          <t>Thời Gian Tích Điện</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Leihuang Master Concerto Regen</t>
+          <t>Khúc Tái Sinh Concerto Lôi Hoàng</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>DMG Illuminous Epiphany: Stella Glamor</t>
+          <t>Khải Tường: Stella Glamor DMG</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Tiêu hao STA của Heavy Attack</t>
+          <t>HA Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>DMG Cogitation Model</t>
+          <t>Sát Thương Mô Hình Suy Tưởng</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Pivot - Đâm Xuyên Stage 2 Sát Thương</t>
+          <t>Pivot - Đâm Xuyên Giai Đoạn 2 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Pivot - Đâm Xuyên Stage 3 Sát Thương</t>
+          <t>Pivot - Đâm Xuyên Giai Đoạn 3 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>DMG Divergence</t>
+          <t>Sát Thương Khúc Giao Dị</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>DMG Unfathomed</t>
+          <t>DMG bí ẩn</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Thời gian Intuition</t>
+          <t>Thời gian Trực giác</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Cooldown Mô Hình Suy Tư</t>
+          <t>Hồi Chiêu Mô Hình Suy Tư</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Cooldown Khúc Giao Dị</t>
+          <t>Hồi Chiêu Khúc Giao Dị</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Cogitation Model Concerto Regen</t>
+          <t>Hồi Phục Bản Giao Hưởng Mô Hình Suy Tư</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>DMG Decipher</t>
+          <t>DMG Giải Mã</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>DMG Law of Reigns</t>
+          <t>Luật Thống Trị: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>DMG Revamp</t>
+          <t>Tăng Sát Thương Cải Tiến</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Tiêu hao STA của Revamp</t>
+          <t>Giảm Tiêu Hao STA Cải Tiến</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Decipher Concerto Regen</t>
+          <t>Hồi phục Khúc Giao Hưởng Giải Mã</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Law of Reigns Concerto Regen</t>
+          <t>Luật Thống Trị: Hồi Phục Khúc Concerto</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Revamp Concerto Regen</t>
+          <t>Bản Concerto Cải Tiến - Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Divergence Concerto Regen</t>
+          <t>Hồi Phục Khúc Giao Dị</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Heavy Attack: Sát Thương Thép Va Đập</t>
+          <t>Đòn Heavy Attack: Steelclash DMG</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Heavy Attack: Tiêu Hao STA Thép Va Đập</t>
+          <t>Đòn Heavy Attack: Steelclash  STA Cost</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sấm Gầm: Sát Thương Lùi Bước</t>
+          <t>Tấn Công Mạnh - Sấm Gầm: Backstep DMG</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sấm Gầm: Sát Thương Xoay Kiếm</t>
+          <t>Tấn Công Mạnh - Sấm Gầm: Spinslash DMG</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sấm Gầm: Sát Thương Móc Lên</t>
+          <t>Tấn Công Mạnh - Sấm Gầm: Uppercut DMG</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Resonance Skill - Ánh Dương Bất Tử: Sát Thương Đòn Đánh</t>
+          <t>Resonance Skill - Ánh Dương Bất Tử: Strike DMG</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Resonance Skill - Ánh Dương Bất Tử: Sát Thương Nhảy</t>
+          <t>Resonance Skill - Ánh Dương Bất Tử: Leap DMG</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Resonance Skill - Ánh Dương Bất Tử: Sát Thương Đâm Xuống</t>
+          <t>Resonance Skill - Ánh Dương Bất Tử: Plunge DMG</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Dodge Counter - Sát thương Heavy Attack: Va Đập Thép</t>
+          <t>Phản đòn né tránh - DMG Tấn Công Mạnh: Steelclash DMG</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Dodge Phán Công - Hồi Âm Sấm Sét: Sát Thương Lùi Bước</t>
+          <t>Né Tránh Phán Công - Hồi Âm Sấm Sét: Backstep DMG</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Dodge Counter Trên Không - Undying Sunlight: Sát Thương Đòn Đánh</t>
+          <t>Dodge Counter Tránh Trên Không - Undying Sunlight: Strike DMG</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Resonance Skill - Ánh Dương Bất Tử: Hồi Phục Khúc Concerto Đâm Xuống</t>
+          <t>Resonance Skill - Ánh Dương Bất Tử: Plunge Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sấm Gầm: Xoay Kiếm Tiêu Hao STA</t>
+          <t>Tấn Công Mạnh - Sấm Gầm: Spinslash STA Cost</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sấm Gầm: Móc Lên Tiêu Hao STA</t>
+          <t>Tấn Công Mạnh - Sấm Gầm: Uppercut STA Cost</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Cooldown Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu</t>
+          <t>Hồi Chiêu Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Chi Phí Resonatori Phóng - Kiếm Lời Thề Vĩnh Cửu</t>
+          <t>Chi Phí Cộng Hưởng Giải Phóng - Kiếm Lời Thề Vĩnh Cửu</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Resonance Liberation - Mặt Trời Cao Cả Cooldown</t>
+          <t>Resonance Liberation - Mặt Trời Cao Cả Hồi Chiêu</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>DMG từ Mid-air Dodge Counter</t>
+          <t>Sát Thương Dodge Counter Tránh Trên Không</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Tiêu hao STA của Mid-air Dodge Counter</t>
+          <t>Tiêu Hao STA Dodge Counter Tránh Trên Không</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Resonance Skill - Ánh Dương Bất Tử: Chi Phí Thể Lực Đòn Đánh</t>
+          <t>Resonance Skill - Ánh Dương Bất Tử: Strike STA Cost</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Resonance Skill - Ánh Dương Bất Tử: Tiêu Hao Thể Lực Nhảy</t>
+          <t>Resonance Skill - Ánh Dương Bất Tử: Leap STA Cost</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Heavy Attack - Linh Môn Chi Mộng: Chi Phí Thể Lực</t>
+          <t>Tấn Công Mạnh - Linh Môn Chi Mộng: Chi Phí STA</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>DMG Undaunted Wayfarer</t>
+          <t>Sát Thương Bản Giao Hưởng Lữ Khách Bất Khuất</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Undaunted Wayfarer Concerto Regen</t>
+          <t>Hồi Phục Bản Giao Hưởng Lữ Khách Bất Khuất</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>DMG kỹ năng</t>
+          <t>Sát thương Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Dodge Counter Concerto Regen</t>
+          <t>Né Tránh Phản Công Hồi Phục Năng Lượng Giao Hưởng</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc Stage 1 Sát Thương</t>
+          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc Giai Đoạn 1 Sát Thương</t>
         </is>
       </c>
     </row>
